--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0066.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0066.xlsx
@@ -21652,7 +21652,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21722,7 +21722,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Throw</t>
+          <t>Ném</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Đặt Xuống</t>
+          <t>Đặt xuống đi</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21862,7 +21862,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Rotate</t>
+          <t>Xoay</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Aim</t>
+          <t>Ngắm</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22072,7 +22072,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Kích hoạt nút điều kiện trước để mở khóa</t>
+          <t>Kích hoạt nút điều kiện để mở khóa</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Hình Dạng Sương Mù: Vào trạng thái Hình Dạng Sương Mù sau khi vượt qua "Sương Mù"</t>
+          <t>Hình Sương: Tiến vào trạng thái Hình Sương sau khi đi qua "Sương Mù"</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22842,7 +22842,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Ở Chế Độ Hỏa Ngục, với ít nhất 30 Ngọn Lửa, mở khóa các động tác sau:</t>
+          <t>Trong Chế Độ Hỏa Ngục, với ít nhất 30 Blazes, mở khóa các động tác sau:</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22912,7 +22912,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Khi không ở Chế Độ Hỏa Ngục, với năng lượng Redundant tối đa, mở khóa các động tác sau:</t>
+          <t>Khi không ở Chế Độ Hỏa Ngục, với Năng Lượng Dư Thừa tối đa, mở khóa các đòn đánh sau:</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22982,7 +22982,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Electro Flare Effect</t>
+          <t>Hiệu Ứng Điện Quang</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Healing</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23122,7 +23122,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Shield</t>
+          <t>Khiên</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Time Stop</t>
+          <t>Thời gian dừng lại</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Vibration Strength Reduction</t>
+          <t>Giảm Cường Độ Rung Động</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23332,7 +23332,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Summon</t>
+          <t>Triệu hồi</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Healing Bonus+</t>
+          <t>Hiệu ứng hồi phục+</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23472,7 +23472,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Healing Bonus+</t>
+          <t>Hiệu ứng hồi phục+</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23542,7 +23542,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Healing Bonus+</t>
+          <t>Hiệu ứng hồi phục+</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Healing Bonus+</t>
+          <t>Hiệu ứng hồi phục+</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23682,7 +23682,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Healing Bonus+</t>
+          <t>Hiệu ứng hồi phục+</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23752,7 +23752,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Healing Bonus+</t>
+          <t>Hiệu ứng hồi phục+</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23822,7 +23822,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Healing Bonus+</t>
+          <t>Hiệu ứng hồi phục+</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23892,7 +23892,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Healing Bonus+</t>
+          <t>Hiệu ứng hồi phục+</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -23962,7 +23962,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Tune Break</t>
+          <t>Đột phá Điệu nhạc</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24032,7 +24032,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Thưởng Chỉ Số</t>
+          <t>Tăng thuộc tính</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -30472,7 +30472,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -35372,7 +35372,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35442,7 +35442,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35512,7 +35512,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Radiant Dawn</t>
+          <t>Bình Minh Rực Rỡ</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
